--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:10</t>
+    <t xml:space="preserve">2026-09-24 01:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>-0.08</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.27</v>
@@ -584,10 +584,10 @@
         <v>-0.16</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="4">
@@ -607,10 +607,10 @@
         <v>0.02</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>0.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.46</v>
@@ -653,10 +653,10 @@
         <v>0.21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="7">
@@ -667,7 +667,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>9</v>
@@ -676,10 +676,10 @@
         <v>-0.05</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="8">
@@ -690,19 +690,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         <v>-0.13</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.92</v>
@@ -768,10 +768,10 @@
         <v>-0.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="12">
@@ -782,7 +782,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>9</v>
@@ -791,7 +791,7 @@
         <v>0.11</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.15</v>
@@ -811,13 +811,13 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="14">
@@ -828,16 +828,16 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.1</v>
@@ -851,19 +851,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -883,7 +883,7 @@
         <v>0.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.08</v>
@@ -897,7 +897,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>9</v>
@@ -906,7 +906,7 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.03</v>
@@ -929,7 +929,7 @@
         <v>-0.32</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.33</v>
@@ -943,7 +943,7 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>9</v>
@@ -952,10 +952,10 @@
         <v>0.23</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="20">
@@ -972,13 +972,13 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21">
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>9</v>
@@ -998,10 +998,10 @@
         <v>0.01</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:00</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_atacama.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
